--- a/artfynd/A 14421-2024 artfynd.xlsx
+++ b/artfynd/A 14421-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117781107</v>
       </c>
       <c r="B2" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 14421-2024 artfynd.xlsx
+++ b/artfynd/A 14421-2024 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119742129</v>
+        <v>119742706</v>
       </c>
       <c r="B4" t="n">
-        <v>8421</v>
+        <v>96856</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,23 +911,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>221944</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -971,11 +967,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119742706</v>
+        <v>119742129</v>
       </c>
       <c r="B5" t="n">
-        <v>96856</v>
+        <v>8421</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,19 +1009,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221944</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1074,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14421-2024 artfynd.xlsx
+++ b/artfynd/A 14421-2024 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119742706</v>
+        <v>119742129</v>
       </c>
       <c r="B4" t="n">
-        <v>96856</v>
+        <v>8421</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,19 +911,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221944</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -967,6 +971,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119742129</v>
+        <v>119742706</v>
       </c>
       <c r="B5" t="n">
-        <v>8421</v>
+        <v>96856</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,23 +1018,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>221944</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1069,11 +1074,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14421-2024 artfynd.xlsx
+++ b/artfynd/A 14421-2024 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119742129</v>
+        <v>119742706</v>
       </c>
       <c r="B4" t="n">
-        <v>8421</v>
+        <v>96879</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,23 +911,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>221944</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -971,11 +967,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119742706</v>
+        <v>119742129</v>
       </c>
       <c r="B5" t="n">
-        <v>96856</v>
+        <v>8421</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,19 +1009,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221944</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1074,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14421-2024 artfynd.xlsx
+++ b/artfynd/A 14421-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119742706</v>
+        <v>119742129</v>
       </c>
       <c r="B4" t="n">
-        <v>96879</v>
+        <v>8421</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,19 +911,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221944</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -969,6 +973,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -990,113 +999,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>119742129</v>
-      </c>
-      <c r="B5" t="n">
-        <v>8421</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>106554</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Slättås, Slättås, Vg</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>333643</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6395225</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Härryda</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Landvetter</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spår</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14421-2024 artfynd.xlsx
+++ b/artfynd/A 14421-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117781107</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
